--- a/data/emptyspace.xlsx
+++ b/data/emptyspace.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/chloeedwards_tudelft_nl/Documents/Documents/GitHub/Digital-Twin-3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{21B08916-1BD2-4732-92A8-8421AD5A9288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B851D7-9864-4068-A703-4A665EF5CE59}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{21B08916-1BD2-4732-92A8-8421AD5A9288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C209736D-F10D-41EA-B72C-0D2F27856166}"/>
   <bookViews>
-    <workbookView xWindow="22275" yWindow="-12585" windowWidth="21600" windowHeight="11175" xr2:uid="{4B1CBE11-476F-424F-AA1E-E50E55F321CD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4B1CBE11-476F-424F-AA1E-E50E55F321CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -646,10 +646,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
+        <v>176</v>
+      </c>
+      <c r="B12">
         <v>178</v>
-      </c>
-      <c r="B12">
-        <v>180</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
